--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
@@ -246,9 +246,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -286,7 +286,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -392,7 +392,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -534,7 +534,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -542,6 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6050695-7AD5-4EAF-ACCC-796FB129457A}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jevans8\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CA5E8E-A54C-4860-B017-C7DC9575D383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21EFB29-6388-4B1D-AFC4-15AAA8E0DF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>Jul 2024 - Jun 2025 (14/10/25)</t>
   </si>
   <si>
-    <t>Jul 2025 (29/08/25)</t>
-  </si>
-  <si>
     <t>Mar 2025 (14/10/24)</t>
   </si>
   <si>
@@ -143,9 +140,6 @@
     <t>Oct 2024 - Sep 2025 (20/01/26)</t>
   </si>
   <si>
-    <t>TBC*</t>
-  </si>
-  <si>
     <t>Dec 2023 - Dec 2024 (20/11/25)</t>
   </si>
   <si>
@@ -162,6 +156,12 @@
   </si>
   <si>
     <t>Aug 2025 – Jul 2026 (Nov 26)</t>
+  </si>
+  <si>
+    <t>Nov 2025 (23/12/25)</t>
+  </si>
+  <si>
+    <t>Dec 2025 (Jan 26)</t>
   </si>
 </sst>
 </file>
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.35">
@@ -585,7 +585,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -599,7 +599,7 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.35">
@@ -607,13 +607,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -621,13 +621,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -652,10 +652,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -666,10 +666,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -680,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -691,13 +691,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,13 +705,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -722,10 +722,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-1_DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21EFB29-6388-4B1D-AFC4-15AAA8E0DF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D75A151-E2FF-4B82-93EE-270BCC805CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="1900" yWindow="740" windowWidth="20660" windowHeight="14300" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>Data​</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>Jan 2025 - Dec 2025 (Apr 26)</t>
-  </si>
-  <si>
-    <t>Jul 2024 - Jun 2025 (14/10/25)</t>
   </si>
   <si>
     <t>Mar 2025 (14/10/24)</t>
@@ -568,10 +565,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.35">
@@ -582,10 +579,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -596,10 +593,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.35">
@@ -607,13 +604,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -621,13 +618,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -652,10 +649,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -666,10 +663,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -680,10 +677,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -691,13 +688,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,13 +702,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -722,10 +719,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
         <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-1_DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D75A151-E2FF-4B82-93EE-270BCC805CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1D75A151-E2FF-4B82-93EE-270BCC805CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87491967-A868-4943-8D07-3B402C63C8CD}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="740" windowWidth="20660" windowHeight="14300" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (16/10/25)</t>
   </si>
   <si>
-    <t>Aug 2023 -  Jul 2024 (22/23 learners) (Feb 26)</t>
-  </si>
-  <si>
     <t>Oct 2024 - Sep 2025 (20/01/26)</t>
   </si>
   <si>
@@ -158,7 +155,10 @@
     <t>Nov 2025 (23/12/25)</t>
   </si>
   <si>
-    <t>Dec 2025 (Jan 26)</t>
+    <t>Aug 2023 -  Jul 2024 (22/23 learners) (Mar 26)</t>
+  </si>
+  <si>
+    <t>Jan 2025 (Feb 26)</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -579,7 +579,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -593,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -604,13 +604,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -618,13 +618,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -677,10 +677,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -694,7 +694,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -708,7 +708,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-1_DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1D75A151-E2FF-4B82-93EE-270BCC805CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87491967-A868-4943-8D07-3B402C63C8CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE8CEB-6D67-456F-ADBE-A57DA970F725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -152,13 +152,13 @@
     <t>Aug 2025 – Jul 2026 (Nov 26)</t>
   </si>
   <si>
-    <t>Nov 2025 (23/12/25)</t>
-  </si>
-  <si>
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (Mar 26)</t>
   </si>
   <si>
-    <t>Jan 2025 (Feb 26)</t>
+    <t>Jan 2026 (27/02/26)</t>
+  </si>
+  <si>
+    <t>Feb 2026 (Mar 26)</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -708,7 +708,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-1_DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EE8CEB-6D67-456F-ADBE-A57DA970F725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397B93E5-4144-499E-918B-2CB87CFF9ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/key-stage-4-destination-measures/'&gt;Key stage 4 destination measures&lt;/a&gt;</t>
   </si>
   <si>
-    <t>Aug 2023 -  Jul 2024 (22/23 learners) (16/10/25)</t>
-  </si>
-  <si>
     <t>Oct 2024 - Sep 2025 (20/01/26)</t>
   </si>
   <si>
@@ -155,10 +152,13 @@
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (Mar 26)</t>
   </si>
   <si>
-    <t>Jan 2026 (27/02/26)</t>
-  </si>
-  <si>
-    <t>Feb 2026 (Mar 26)</t>
+    <t>Feb 2026 (30/03/26)</t>
+  </si>
+  <si>
+    <t>Mar 2026 (24/04/26)</t>
+  </si>
+  <si>
+    <t>Aug 2023 -  Jul 2024 (22/23 learners) (26/03/26)</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -579,7 +579,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -593,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -604,13 +604,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -618,13 +618,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -677,10 +677,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -691,10 +691,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,10 +705,10 @@
         <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -719,10 +719,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397B93E5-4144-499E-918B-2CB87CFF9ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -149,9 +149,6 @@
     <t>Aug 2025 – Jul 2026 (Nov 26)</t>
   </si>
   <si>
-    <t>Aug 2023 -  Jul 2024 (22/23 learners) (Mar 26)</t>
-  </si>
-  <si>
     <t>Feb 2026 (30/03/26)</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (26/03/26)</t>
+  </si>
+  <si>
+    <t>Aug 2023 -  Jul 2024 (22/23 learners) (tbc)</t>
   </si>
 </sst>
 </file>
@@ -691,10 +691,10 @@
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,10 +705,10 @@
         <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -719,10 +719,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -743,5 +743,15 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL - FOR PUBLIC RELEASE&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL - FOR PUBLIC RELEASE</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{dbf2ff9d-e249-40e2-b463-0b922d4f2f25}" enabled="1" method="Privileged" siteId="{fad277c9-c60a-4da1-b5f3-b3b8b34a82f9}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-1_DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC9CCE9B-45FD-4B0A-AACC-A7C0A0466434}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>Data​</t>
   </si>
@@ -110,9 +110,6 @@
     <t>2035 (05/08/24)</t>
   </si>
   <si>
-    <t>Jan 2024 - Dec 2024 (15/04/25)</t>
-  </si>
-  <si>
     <t>Jan 2025 - Dec 2025 (Apr 26)</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/key-stage-4-destination-measures/'&gt;Key stage 4 destination measures&lt;/a&gt;</t>
   </si>
   <si>
-    <t>Oct 2024 - Sep 2025 (20/01/26)</t>
-  </si>
-  <si>
     <t>Dec 2023 - Dec 2024 (20/11/25)</t>
   </si>
   <si>
@@ -159,6 +153,9 @@
   </si>
   <si>
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (tbc)</t>
+  </si>
+  <si>
+    <t>April 2025 - Mar 2026 (TBC)</t>
   </si>
 </sst>
 </file>
@@ -565,10 +562,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.35">
@@ -579,10 +576,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -593,10 +590,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.35">
@@ -604,13 +601,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -618,13 +615,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -638,7 +635,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -649,10 +646,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -663,10 +660,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -677,10 +674,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -688,13 +685,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -702,13 +699,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -719,10 +716,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC9CCE9B-45FD-4B0A-AACC-A7C0A0466434}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D70FA9-1DA0-472D-9218-E1429AD6A4EA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -143,12 +143,6 @@
     <t>Aug 2025 – Jul 2026 (Nov 26)</t>
   </si>
   <si>
-    <t>Feb 2026 (30/03/26)</t>
-  </si>
-  <si>
-    <t>Mar 2026 (24/04/26)</t>
-  </si>
-  <si>
     <t>Aug 2023 -  Jul 2024 (22/23 learners) (26/03/26)</t>
   </si>
   <si>
@@ -156,6 +150,12 @@
   </si>
   <si>
     <t>April 2025 - Mar 2026 (TBC)</t>
+  </si>
+  <si>
+    <t>Apr 2026 (22/05/26)</t>
+  </si>
+  <si>
+    <t>May 2026 (June 2026)</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.35">
@@ -579,7 +579,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -593,7 +593,7 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.35">
@@ -635,7 +635,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -688,10 +688,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -702,10 +702,10 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
@@ -716,10 +716,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D70FA9-1DA0-472D-9218-E1429AD6A4EA}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D322B151-E5AF-44D5-BDD3-7EE764637753}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -152,10 +152,10 @@
     <t>April 2025 - Mar 2026 (TBC)</t>
   </si>
   <si>
-    <t>Apr 2026 (22/05/26)</t>
-  </si>
-  <si>
-    <t>May 2026 (June 2026)</t>
+    <t>May 2026 (26/06/26)</t>
+  </si>
+  <si>
+    <t>June 2026 (July 2026)</t>
   </si>
 </sst>
 </file>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D322B151-E5AF-44D5-BDD3-7EE764637753}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530D27F9-136A-455C-999C-FC6AECF97A39}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -152,10 +152,10 @@
     <t>April 2025 - Mar 2026 (TBC)</t>
   </si>
   <si>
-    <t>May 2026 (26/06/26)</t>
-  </si>
-  <si>
-    <t>June 2026 (July 2026)</t>
+    <t>Jun 2026 (24/07/26)</t>
+  </si>
+  <si>
+    <t>July 2026 (Aug 2026)</t>
   </si>
 </sst>
 </file>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530D27F9-136A-455C-999C-FC6AECF97A39}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFE5B48-4D29-4031-B9C5-11DE375EC3CB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
@@ -152,10 +152,10 @@
     <t>April 2025 - Mar 2026 (TBC)</t>
   </si>
   <si>
-    <t>Jun 2026 (24/07/26)</t>
-  </si>
-  <si>
-    <t>July 2026 (Aug 2026)</t>
+    <t>Jul 2026 (21/08/26)</t>
+  </si>
+  <si>
+    <t>August 2026 (Sep 2026)</t>
   </si>
 </sst>
 </file>

--- a/Data/3-1_DataTable/DataTable.xlsx
+++ b/Data/3-1_DataTable/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-1_DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFE5B48-4D29-4031-B9C5-11DE375EC3CB}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{BB966AC7-D478-46F4-96D8-4ADE6513DE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DEE3EBA-6B8C-41C5-92E4-ED52225FAEF6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
+    <workbookView xWindow="1820" yWindow="20" windowWidth="20660" windowHeight="14300" xr2:uid="{677CE7B9-0003-4845-87B7-4FABD7ACD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Data​</t>
   </si>
@@ -156,6 +156,12 @@
   </si>
   <si>
     <t>August 2026 (Sep 2026)</t>
+  </si>
+  <si>
+    <t>April 2025 - Mar 2026 (Sep 26)</t>
+  </si>
+  <si>
+    <t>July 2025 - June 2026 (TBC)</t>
   </si>
 </sst>
 </file>
@@ -562,10 +568,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.35">
@@ -576,10 +582,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -590,10 +596,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.35">
